--- a/Excel Files/Regional sales.xlsx
+++ b/Excel Files/Regional sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/541318ea739a5681/Desktop/JavaApps/Excel Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{4F2818B8-BE40-4D3A-BB72-155A9209CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395AF9E7-4D0F-4EB0-9795-934D9843C55C}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="8_{4F2818B8-BE40-4D3A-BB72-155A9209CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F1D70D-8192-4113-9061-2DF34EDC6B13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F4D2F806-F586-405E-A4C1-D481A49628C6}"/>
   </bookViews>
@@ -358,7 +358,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +368,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,7 +535,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -659,6 +665,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -1635,10 +1643,10 @@
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
-      <c r="E31" s="50" t="s">
+      <c r="E31" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="50"/>
+      <c r="F31" s="62"/>
       <c r="G31" s="51" t="s">
         <v>58</v>
       </c>
@@ -1677,7 +1685,7 @@
       </c>
       <c r="E32" s="52">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="46" t="s">
@@ -1964,9 +1972,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+      <c r="B44" s="61" t="s">
         <v>72</v>
       </c>
+      <c r="C44" s="61"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D45" s="51" t="s">
@@ -2303,9 +2312,10 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="61" t="s">
         <v>87</v>
       </c>
+      <c r="B54" s="61"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="51" t="s">
@@ -2334,6 +2344,7 @@
       <c r="J55" s="60" t="s">
         <v>94</v>
       </c>
+      <c r="K55" s="59"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="46" t="s">
